--- a/outputs/resultats/td/2026_t1_vs_2025_t3/comparison.xlsx
+++ b/outputs/resultats/td/2026_t1_vs_2025_t3/comparison.xlsx
@@ -2005,7 +2005,9 @@
       <c r="H30" s="4" t="inlineStr"/>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>(1) Le changement est pertinent car il implique la suppression d'un tableau entier lié à la gestion du capital ; (2) Cela peut affecter la transparence et la compréhension des expositions nettes par région et contrepartie, ce qui est crucial pour l'évaluation des risques géographiques ; (3) Il s'agit d'une suppression structurelle qui pourrait indiquer un changement dans la manière dont la banque gère ou divulgue ses expositions.</t>
+          <t>Le changement constaté concerne la suppression d'un tableau intitulé 'TOTAL DE L’EXPOSITION NETTE PAR RÉGION ET CONTREPARTIE' dans la section de gestion du capital. Ce tableau fournissait des informations détaillées sur l'exposition nette de la banque par région, incluant des régions spécifiques comme l'Europe, le Royaume-Uni, l'Asie, et d'autres. La suppression de ce tableau peut indiquer un changement dans la manière dont la banque divulgue ses expositions régionales, ce qui pourrait avoir des implications sur la transparence des risques géographiques et la gestion du capital.
+D'un point de vue réglementaire, la divulgation des expositions par région est souvent requise pour évaluer le risque géographique et la concentration des actifs. La suppression de ce tableau pourrait affecter la capacité des régulateurs et des parties prenantes à évaluer correctement ces risques. Cela pourrait également avoir un impact sur la conformité avec les exigences de divulgation du Pilier 3 de Bâle III, qui vise à promouvoir la transparence et la discipline de marché.
+Il est recommandé d'investiguer ce changement pour comprendre les raisons derrière la suppression de ce tableau. Il pourrait s'agi</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">

--- a/outputs/resultats/td/2026_t1_vs_2025_t3/comparison.xlsx
+++ b/outputs/resultats/td/2026_t1_vs_2025_t3/comparison.xlsx
@@ -2005,9 +2005,9 @@
       <c r="H30" s="4" t="inlineStr"/>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>Le changement constaté concerne la suppression d'un tableau intitulé 'TOTAL DE L’EXPOSITION NETTE PAR RÉGION ET CONTREPARTIE' dans la section de gestion du capital. Ce tableau fournissait des informations détaillées sur l'exposition nette de la banque par région, incluant des régions spécifiques comme l'Europe, le Royaume-Uni, l'Asie, et d'autres. La suppression de ce tableau peut indiquer un changement dans la manière dont la banque divulgue ses expositions régionales, ce qui pourrait avoir des implications sur la transparence des risques géographiques et la gestion du capital.
-D'un point de vue réglementaire, la divulgation des expositions par région est souvent requise pour évaluer le risque géographique et la concentration des actifs. La suppression de ce tableau pourrait affecter la capacité des régulateurs et des parties prenantes à évaluer correctement ces risques. Cela pourrait également avoir un impact sur la conformité avec les exigences de divulgation du Pilier 3 de Bâle III, qui vise à promouvoir la transparence et la discipline de marché.
-Il est recommandé d'investiguer ce changement pour comprendre les raisons derrière la suppression de ce tableau. Il pourrait s'agi</t>
+          <t>Le changement constaté concerne la suppression d'un tableau intitulé 'TOTAL DE L’EXPOSITION NETTE PAR RÉGION ET CONTREPARTIE' dans la section de gestion du capital. Ce tableau fournissait des informations détaillées sur l'exposition nette de la banque par région, incluant des régions spécifiques comme l'Europe, le Royaume-Uni, l'Asie, et d'autres. La suppression de ce tableau peut indiquer un changement dans la manière dont la banque divulgue ses expositions géographiques, ce qui pourrait avoir des implications sur la transparence et la gestion des risques géographiques.
+D'un point de vue réglementaire, la divulgation des expositions par région est souvent requise pour évaluer la concentration des risques et la diversification géographique, ce qui est crucial pour le respect des exigences de Bâle III en matière de gestion des risques. La suppression de ce tableau pourrait signifier un changement dans la stratégie de divulgation ou une révision des méthodes de calcul des expositions, ce qui nécessite une attention particulière pour s'assurer que la banque reste conforme aux attentes réglementaires.
+Il est recommandé d'investiguer ce changement pour comprendre les raisons derrière</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">

--- a/outputs/resultats/td/2026_t1_vs_2025_t3/comparison.xlsx
+++ b/outputs/resultats/td/2026_t1_vs_2025_t3/comparison.xlsx
@@ -2005,9 +2005,9 @@
       <c r="H30" s="4" t="inlineStr"/>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>Le changement constaté concerne la suppression d'un tableau intitulé 'TOTAL DE L’EXPOSITION NETTE PAR RÉGION ET CONTREPARTIE' dans la section de gestion du capital. Ce tableau fournissait des informations détaillées sur l'exposition nette de la banque par région, incluant des régions spécifiques comme l'Europe, le Royaume-Uni, l'Asie, et d'autres. La suppression de ce tableau peut indiquer un changement dans la manière dont la banque divulgue ses expositions géographiques, ce qui pourrait avoir des implications sur la transparence et la gestion des risques géographiques.
-D'un point de vue réglementaire, la divulgation des expositions par région est souvent requise pour évaluer la concentration des risques et la diversification géographique, ce qui est crucial pour le respect des exigences de Bâle III en matière de gestion des risques. La suppression de ce tableau pourrait signifier un changement dans la stratégie de divulgation ou une révision des méthodes de calcul des expositions, ce qui nécessite une attention particulière pour s'assurer que la banque reste conforme aux attentes réglementaires.
-Il est recommandé d'investiguer ce changement pour comprendre les raisons derrière</t>
+          <t>Le changement constaté concerne la suppression d'un tableau intitulé 'TOTAL DE L’EXPOSITION NETTE PAR RÉGION ET CONTREPARTIE' dans la section de gestion du capital. Ce tableau fournissait des informations détaillées sur l'exposition nette de la banque par région, incluant l'Europe, le Royaume-Uni, l'Asie, et d'autres régions. La suppression de ce tableau peut indiquer un changement dans la manière dont la banque divulgue ses expositions géographiques, ce qui pourrait avoir des implications sur la transparence et la compréhension des risques géographiques par les parties prenantes.
+D'un point de vue réglementaire, la divulgation des expositions par région est souvent requise pour évaluer la concentration des risques et la diversification géographique, conformément aux exigences de Bâle III et aux lignes directrices du BSIF. La suppression de ce tableau pourrait donc affecter la capacité des régulateurs et des investisseurs à évaluer correctement le profil de risque de la banque. Il est crucial de comprendre si cette suppression est compensée par d'autres divulgations ou si elle résulte d'un changement méthodologique.
+Il est recommandé d'investiguer ce changement pour déterminer s'</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">

--- a/outputs/resultats/td/2026_t1_vs_2025_t3/comparison.xlsx
+++ b/outputs/resultats/td/2026_t1_vs_2025_t3/comparison.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Changements détectés" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Changements détectés'!$A$1:$K$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Changements détectés'!$A$1:$N$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:N30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -471,6 +471,9 @@
     <col width="70" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -529,6 +532,21 @@
           <t>Commentaire analyste</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Statut validation</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Validé par</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Validé le</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -582,6 +600,9 @@
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -631,6 +652,21 @@
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-18T18:09:11.852867+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -684,6 +720,21 @@
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr"/>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-18T18:08:54.256438+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -737,6 +788,21 @@
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr"/>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-18T18:08:51.689245+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -790,6 +856,9 @@
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr"/>
+      <c r="L6" s="3" t="inlineStr"/>
+      <c r="M6" s="3" t="inlineStr"/>
+      <c r="N6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -843,6 +912,21 @@
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr"/>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-18T18:09:23.972718+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -896,6 +980,9 @@
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr"/>
+      <c r="L8" s="3" t="inlineStr"/>
+      <c r="M8" s="3" t="inlineStr"/>
+      <c r="N8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -945,6 +1032,21 @@
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr"/>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-18T18:07:41.005371+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -998,6 +1100,21 @@
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr"/>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-18T18:09:31.829097+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -1051,6 +1168,9 @@
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr"/>
+      <c r="L11" s="3" t="inlineStr"/>
+      <c r="M11" s="3" t="inlineStr"/>
+      <c r="N11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1100,6 +1220,21 @@
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr"/>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-18T18:08:21.346716+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -1153,6 +1288,21 @@
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr"/>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-18T18:09:20.442659+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -1206,6 +1356,21 @@
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr"/>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-18T18:09:20.590280+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -1259,6 +1424,9 @@
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr"/>
+      <c r="L15" s="3" t="inlineStr"/>
+      <c r="M15" s="3" t="inlineStr"/>
+      <c r="N15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -1308,6 +1476,21 @@
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr"/>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-18T18:09:09.274937+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -1361,6 +1544,9 @@
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
+      <c r="L17" s="3" t="inlineStr"/>
+      <c r="M17" s="3" t="inlineStr"/>
+      <c r="N17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -1410,6 +1596,21 @@
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr"/>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-18T18:07:24.685574+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -1463,6 +1664,21 @@
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr"/>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-18T18:09:12.321942+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -1516,6 +1732,9 @@
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr"/>
+      <c r="L20" s="3" t="inlineStr"/>
+      <c r="M20" s="3" t="inlineStr"/>
+      <c r="N20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -1569,6 +1788,9 @@
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr"/>
+      <c r="L21" s="3" t="inlineStr"/>
+      <c r="M21" s="3" t="inlineStr"/>
+      <c r="N21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -1622,6 +1844,9 @@
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr"/>
+      <c r="L22" s="3" t="inlineStr"/>
+      <c r="M22" s="3" t="inlineStr"/>
+      <c r="N22" s="3" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -1675,6 +1900,9 @@
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr"/>
+      <c r="L23" s="3" t="inlineStr"/>
+      <c r="M23" s="3" t="inlineStr"/>
+      <c r="N23" s="3" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -1724,6 +1952,21 @@
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr"/>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-18T18:07:36.224563+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -1773,6 +2016,21 @@
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr"/>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-18T18:09:04.945140+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -1822,6 +2080,21 @@
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr"/>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-18T18:09:11.928472+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -1871,6 +2144,21 @@
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr"/>
+      <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M27" s="4" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N27" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-18T18:09:37.640911+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -1920,6 +2208,21 @@
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr"/>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M28" s="4" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N28" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-18T18:08:29.024930+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -1969,6 +2272,21 @@
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr"/>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M29" s="4" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N29" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-18T18:08:34.008361+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -2016,9 +2334,12 @@
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr"/>
+      <c r="L30" s="4" t="inlineStr"/>
+      <c r="M30" s="4" t="inlineStr"/>
+      <c r="N30" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K30"/>
+  <autoFilter ref="A1:N30"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/resultats/td/2026_t1_vs_2025_t3/comparison.xlsx
+++ b/outputs/resultats/td/2026_t1_vs_2025_t3/comparison.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Changements détectés" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Changements détectés'!$A$1:$N$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Changements détectés'!$A$1:$N$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N30"/>
+  <dimension ref="A1:N32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -556,42 +556,40 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>RATIOS CIBLES DE FONDS PROPRES RÉGLEMENTAIRES ET DE TLAC</t>
+          <t>STRUCTURE DE FONDS PROPRES ET RATIOS – Bâle III</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>38</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>33</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Note de bas de page</t>
+          <t>Indicateur</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Le plus élevé des suppléments pour les BISI et les banques d’importance systémique mondiale (BISM) s’applique aux fonds propres pondérés en fonction des risques. Le supplément pour les BISI est actuellement équivalent à l’exigence supplémentaire de 1 % relative au ratio de fonds propres sous forme d’actions ordinaires pour les fonds propres pondérés en fonction des risques pour les BISM que doit respecter la Banque. Le supplément pour les BISM pourrait augmenter au-delà de 1 %, si la cote pour les BISM attribuée à la Banque devait augmenter au-delà de certains seuils, pour atteindre un maximum de 4,5 %. La ligne directrice Exigences de levier du BSIF comprend une exigence selon laquelle les BISI doivent maintenir un coussin de ratio de levier fixé à 50 % des exigences pondérées de capacité accrue d’absorption des pertes d’une BISI, soit 0,50 %. Ce coussin s’applique également au ratio de levier TLAC.</t>
-        </is>
-      </c>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Le plus élevé des suppléments pour les BISI et les BISM s’applique aux fonds propres pondérés en fonction des risques. Le supplément pour les BISI est actuellement équivalent à l’exigence supplémentaire de 1 % relative au ratio de fonds propres sous forme d’actions ordinaires pour les fonds propres pondérés en fonction des risques que doit respecter la Banque. Le supplément pour les BISM pourrait augmenter au-delà de 1 %, pour atteindre un maximum de 4 %, si la cote pour les BISM attribuée à la Banque devait augmenter au-delà de certains seuils. La ligne directrice Exigences de levier du BSIF comprend une exigence selon laquelle les BISI doivent maintenir un coussin de ratio de levier fixé à 50 % des exigences pondérées de capacité accrue d’absorption des pertes d’une BISI, soit 0,50 %. Ce coussin s’applique également au ratio de levier TLAC.</t>
+          <t>Déduction des expositions sur crypto-actifs</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>The reduction in the maximum potential increase for the BISM supplement from 4.5% to 4% represents a significant regulatory change that could impact the bank's capital planning and risk management strategies.</t>
+          <t>L'indicateur "Déduction des expositions sur crypto-actifs" a été ajouté dans le tableau de gestion du capital au T1 2026, alors qu'il était absent au T3 2025.
+Cet ajout est significatif car il reflète une nouvelle exigence de divulgation potentiellement liée à l'évolution des réglementations sur les actifs numériques. Les régulateurs, tels que le BSIF, pourraient exiger que les institutions financières déduisent les expositions sur crypto-actifs de leurs fonds propres pour mieux évaluer les risques associés à ces actifs volatils.
+Il s'agit d'une nouvelle divulgation réglementaire. L'analyste devrait confirmer que cette déduction est conforme aux directives réglementaires actuelles et évaluer son impact sur les ratios de fonds propres.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -605,68 +603,62 @@
       <c r="N2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Gestion du capital</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>STRUCTURE DE FONDS PROPRES ET RATIOS – Bâle III</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Indicateur</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Déduction des expositions sur crypto-actifs</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>The addition of a new indicator related to crypto-assets suggests a regulatory change or new risk management practice, which is critical for compliance and risk assessment.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-18T18:09:11.852867+00:00</t>
-        </is>
-      </c>
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>ACTIFS GREVÉS ET ACTIFS NON GREVÉS</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Note de bas de page</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Les sûretés données en garanties correspondent aux actifs donnés en garanties dans le cadre de diverses opérations, telles que des mises en pension, des prêts de valeurs mobilières, des contrats de dérivés, et des exigences liées à la participation aux chambres de compensation et aux systèmes de paiement.</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Les sûretés données en garantie correspondent à la portion des actifs donnés en garantie dans le cadre de grèvement, comme les mises en pension, les prêts de valeurs mobilières, les contrats de dérivés, et les exigences liées à la participation aux chambres de compensation et aux systèmes de paiement.</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>La note de bas de page n°1 a subi une reformulation significative dans le tableau des actifs grevés et non grevés. Le texte a été modifié pour préciser que les sûretés données en garantie correspondent à une portion des actifs, et non à l'ensemble des actifs, dans le cadre de grèvement. Cette distinction est importante car elle clarifie la portée des actifs concernés par les garanties, ce qui peut avoir des implications sur la manière dont ces actifs sont comptabilisés et présentés dans les états financiers.
+Cette modification peut avoir un impact sur la compréhension des engagements de la banque en matière de sûretés, notamment en ce qui concerne les exigences de Bâle III sur la gestion des risques et la transparence des informations financières. En précisant que seule une portion des actifs est concernée, cela pourrait influencer les ratios de levier et de liquidité, ainsi que la perception des risques associés aux opérations de financement et de couverture.
+Il s'agit d'un changement méthodologique significatif qui nécessite une attention particulière. L'analyste devrait confirmer que cette reformulation est cohérente avec les autres divulgations du rapport et qu'elle ne modifie pas de manière substantielle les engagements de la banque. Une vérification supplémentaire pourrait être nécessaire pour s'assurer que cette clarification est correctement intégrée dans les autres sections pertinentes du rapport.</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr"/>
+      <c r="L3" s="3" t="inlineStr"/>
+      <c r="M3" s="3" t="inlineStr"/>
+      <c r="N3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -676,19 +668,19 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>ACTIFS GREVÉS ET ACTIFS NON GREVÉS</t>
+          <t>DURÉE CONTRACTUELLE RESTANTE</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Note de bas de page</t>
@@ -701,17 +693,19 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Les sûretés données en garanties correspondent aux actifs donnés en garanties dans le cadre de diverses opérations, telles que des mises en pension, des prêts de valeurs mobilières, des contrats de dérivés, et des exigences liées à la participation aux chambres de compensation et aux systèmes de paiement.</t>
+          <t>Comprennent 65 milliards de dollars d’obligations sécurisées, dont une tranche de 10 milliards de dollars comporte une durée contractuelle restante de « plus de 6 à 9 mois », une tranche de 3 milliards de dollars comporte une durée contractuelle restante de « plus de 9 mois à 1 an », une tranche de 25 milliards de dollars comporte une durée contractuelle restante de « plus de 1 an à 2 ans », une tranche de 21 milliards de dollars comporte une durée contractuelle restante de « plus de 2 à 5 ans » et une tranche de 6 milliards de dollars comporte une durée contractuelle restante de « plus de 5 ans ».</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Les sûretés données en garantie correspondent à la portion des actifs donnés en garantie dans le cadre de grèvement, comme les mises en pension, les prêts de valeurs mobilières, les contrats de dérivés, et les exigences liées à la participation aux chambres de compensation et aux systèmes de paiement.</t>
+          <t>Comprennent 73 milliards de dollars d’obligations sécurisées, dont une tranche de 10 milliards de dollars comporte une durée contractuelle restante de « plus de 1 mois à 3 mois », une tranche de 3 milliards de dollars comporte une durée contractuelle restante de « plus de 3 à 6 mois », une tranche de 5 milliards de dollars comporte une durée contractuelle restante de « plus de 6 à 9 mois », une tranche de 5 milliards de dollars comporte une durée contractuelle restante de « plus de 9 mois à 1 an », une tranche de 20 milliards de dollars comporte une durée contractuelle restante de « plus de 1 an à 2 ans », une tranche de 22 milliards de dollars comporte une durée contractuelle restante de « plus de 2 à 5 ans » et une tranche de 8 milliards de dollars comporte une durée contractuelle restante de « plus de 5 ans ».</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>The change in wording narrows the scope of the assets considered as collateral, which could impact the bank's risk management and reporting of secured assets.</t>
+          <t>La note de bas de page n°5 a été modifiée dans le tableau de la durée contractuelle restante des actifs, passifs et engagements hors bilan. Le texte a été révisé pour refléter des changements significatifs dans les montants et les durées des obligations sécurisées, passant de 65 milliards de dollars à 73 milliards de dollars, avec des ajustements dans les tranches de durée contractuelle restante.
+Ce changement a un impact structurel important car il modifie la répartition des obligations sécurisées par durée, ce qui peut influencer l'évaluation du risque de liquidité et de refinancement de la banque. Les obligations sécurisées sont souvent utilisées comme garanties dans les opérations de financement, et leur répartition par durée peut affecter la perception du risque par les investisseurs et les régulateurs. En termes de conformité, cela pourrait avoir des implications sur les ratios de liquidité réglementaires tels que le LCR (Liquidity Coverage Ratio) et le NSFR (Net Stable Funding Ratio) selon les normes de Bâle III.
+Il s'agit d'une mise à jour structurelle significative. L'analyste devrait confirmer que ces changements sont correctement intégrés dans les autres sections du rapport financier et vérifier leur cohérence avec les politiques de gestion des risques de la banque. Une attention particulière devrait être portée à l'impact potentiel sur les ratios prudentiels et la communication aux parties prenantes.</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -720,21 +714,9 @@
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr"/>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-18T18:08:54.256438+00:00</t>
-        </is>
-      </c>
+      <c r="L4" s="3" t="inlineStr"/>
+      <c r="M4" s="3" t="inlineStr"/>
+      <c r="N4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -769,40 +751,30 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Comprennent 65 milliards de dollars d’obligations sécurisées, dont une tranche de 10 milliards de dollars comporte une durée contractuelle restante de « plus de 6 à 9 mois », une tranche de 3 milliards de dollars comporte une durée contractuelle restante de « plus de 9 mois à 1 an », une tranche de 25 milliards de dollars comporte une durée contractuelle restante de « plus de 1 an à 2 ans », une tranche de 21 milliards de dollars comporte une durée contractuelle restante de « plus de 2 à 5 ans » et une tranche de 6 milliards de dollars comporte une durée contractuelle restante de « plus de 5 ans ».</t>
+          <t>Comprennent 627 millions de dollars d’engagements de crédit à l’égard de placements dans des actions de sociétés à capital fermé.</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Comprennent 73 milliards de dollars d’obligations sécurisées, dont une tranche de 10 milliards de dollars comporte une durée contractuelle restante de « plus de 1 mois à 3 mois », une tranche de 3 milliards de dollars comporte une durée contractuelle restante de « plus de 3 à 6 mois », une tranche de 5 milliards de dollars comporte une durée contractuelle restante de « plus de 6 à 9 mois », une tranche de 5 milliards de dollars comporte une durée contractuelle restante de « plus de 9 mois à 1 an », une tranche de 20 milliards de dollars comporte une durée contractuelle restante de « plus de 1 an à 2 ans », une tranche de 22 milliards de dollars comporte une durée contractuelle restante de « plus de 2 à 5 ans » et une tranche de 8 milliards de dollars comporte une durée contractuelle restante de « plus de 5 ans ».</t>
+          <t>Comprennent 531 millions de dollars d’engagements de crédit à l’égard de placements dans des actions de sociétés à capital fermé.</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>The change in the distribution and total amount of secured obligations reflects a significant restructuring of financial liabilities, which could impact liquidity management and risk assessment.</t>
+          <t>La note de bas de page n°6 a été modifiée dans le tableau de la durée contractuelle restante des actifs, passifs et engagements hors bilan. Le texte a été révisé pour indiquer une diminution des engagements de crédit à l'égard de placements dans des actions de sociétés à capital fermé, passant de 627 millions de dollars à 531 millions de dollars.
+Ce changement a un impact structurel car il reflète une réduction significative des engagements de crédit dans le secteur des placements privés. Cela peut indiquer une réévaluation des risques associés à ces investissements ou une modification de la stratégie d'investissement de la banque. En termes de conformité, cela pourrait affecter la manière dont la banque gère ses expositions aux risques de crédit et de marché, et pourrait avoir des implications sur les exigences de fonds propres selon les normes de Bâle III.
+Il s'agit d'une mise à jour structurelle importante. L'analyste devrait investiguer les raisons de cette réduction et s'assurer que cela est cohérent avec la stratégie globale de gestion des risques de la banque. Une attention particulière devrait être portée à l'impact potentiel sur les ratios de capital et la communication aux parties prenantes.</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr"/>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-18T18:08:51.689245+00:00</t>
-        </is>
-      </c>
+      <c r="L5" s="3" t="inlineStr"/>
+      <c r="M5" s="3" t="inlineStr"/>
+      <c r="N5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -827,32 +799,30 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Note de bas de page</t>
+          <t>Indicateur</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Modification</t>
+          <t>Suppression</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>Comprennent 627 millions de dollars d’engagements de crédit à l’égard de placements dans des actions de sociétés à capital fermé.</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>Comprennent 531 millions de dollars d’engagements de crédit à l’égard de placements dans des actions de sociétés à capital fermé.</t>
-        </is>
-      </c>
+          <t>Participation dans Schwab</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr"/>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>The reduction in credit commitments to private equity investments suggests a strategic shift or reassessment of risk exposure, which could affect the bank's investment portfolio and risk profile.</t>
+          <t>L'indicateur 'Participation dans Schwab' a été retiré du tableau de la durée contractuelle restante des actifs, passifs et engagements hors bilan. Cet indicateur était précédemment positionné à la 18ème place dans le tableau précédent.
+La suppression de cet indicateur peut avoir un impact significatif sur la transparence des informations financières, notamment en ce qui concerne la divulgation des participations stratégiques dans d'autres entités. Les participations dans des entreprises comme Schwab peuvent influencer les décisions d'investissement et la perception du risque par les parties prenantes. En termes de conformité réglementaire, cela pourrait affecter la manière dont les actifs sont évalués et rapportés, en particulier si ces participations sont considérées comme stratégiques ou influentes.
+Il est recommandé que l'analyste vérifie si cette suppression est due à un changement dans la structure de l'entreprise ou à une modification de la méthodologie de divulgation. Une investigation plus approfondie pourrait être nécessaire pour s'assurer que toutes les obligations de divulgation réglementaires sont respectées et que les parties prenantes sont correctement informées des changements dans les participations de l'entreprise.</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr"/>
@@ -903,7 +873,9 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>The change in the distribution and total amount of secured obligations reflects a significant restructuring of financial liabilities, which could impact liquidity management and risk assessment.</t>
+          <t>La note de bas de page n°5 a subi une révision significative dans le tableau de la durée contractuelle restante des actifs, passifs et engagements hors bilan. Le montant total des obligations sécurisées a été réduit de 75 milliards de dollars à 70 milliards de dollars, et les tranches ont été redistribuées avec des durées contractuelles différentes.
+Ce changement peut avoir un impact sur la perception du risque de liquidité et de la gestion des obligations de la banque. Une réduction du montant total des obligations sécurisées pourrait indiquer une stratégie de désendettement ou une réévaluation des besoins de financement à long terme. Cela pourrait également affecter les ratios de liquidité réglementaires tels que le ratio de liquidité à court terme (LCR) ou le ratio de financement stable net (NSFR) selon les normes de Bâle III.
+Il s'agit d'un changement structurel important qui nécessite une attention particulière. L'analyste devrait confirmer la raison de cette révision avec les équipes de gestion des risques et de la trésorerie pour s'assurer qu'elle est alignée avec la stratégie globale de gestion des risques de la banque. Une investigation plus approfondie pourrait être nécessaire pour comprendre les implications sur les engagements financiers futurs.</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -912,21 +884,9 @@
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr"/>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-18T18:09:23.972718+00:00</t>
-        </is>
-      </c>
+      <c r="L7" s="3" t="inlineStr"/>
+      <c r="M7" s="3" t="inlineStr"/>
+      <c r="N7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -951,27 +911,25 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Note de bas de page</t>
+          <t>Indicateur</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Modification</t>
+          <t>Suppression</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>Comprennent 609 millions de dollars d’engagements de crédit à l’égard de placements dans des actions de sociétés à capital fermé.</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>Comprennent 623 millions de dollars d’engagements de crédit à l’égard de placements dans des actions de sociétés à capital fermé.</t>
-        </is>
-      </c>
+          <t>Participation dans Schwab</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr"/>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>The increase in credit commitments to private equity investments suggests a strategic shift or increased risk exposure, which may affect the bank's capital allocation and risk management strategies.</t>
+          <t>L'indicateur 'Participation dans Schwab' a été retiré du tableau de synthèse des actifs, passifs et engagements hors bilan au T2 2025, alors qu'il était présent au T1 2025.
+Cette suppression peut indiquer un changement dans la structure de participation de la banque, potentiellement lié à une vente ou à une réévaluation de l'investissement dans Schwab. Cela pourrait avoir des implications sur les ratios de capital réglementaire, notamment si cette participation était significative dans le calcul des actifs pondérés en fonction des risques (RWA).
+Il s'agit d'un changement structurel important. L'analyste devrait investiguer la raison de cette suppression et vérifier si elle est liée à une transaction stratégique ou à une réévaluation comptable. Une confirmation avec les équipes de comptabilité ou de gestion des investissements pourrait être nécessaire.</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -992,17 +950,17 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>DURÉE CONTRACTUELLE RESTANTE (suite)</t>
+          <t>FINANCEMENT DE GROS</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>54</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>48</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -1017,36 +975,26 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Participation dans Schwab</t>
+          <t>Dont : – Total</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>The removal of 'Participation dans Schwab' could indicate a significant change in the bank's investment portfolio or strategic partnerships, which may affect financial reporting and risk management strategies.</t>
+          <t>L'indicateur 'Dont : – Total' a été supprimé du tableau actuel de financement de gros, alors qu'il était présent dans le tableau précédent. Cet indicateur servait à fournir une ventilation supplémentaire des totaux, ce qui est crucial pour comprendre la composition des financements garantis et non garantis.
+La suppression de cet indicateur pourrait avoir un impact sur la transparence des rapports financiers, en particulier pour les parties prenantes qui s'appuient sur ces détails pour évaluer la structure de financement de l'institution. Bien que cela ne soit pas directement lié à une exigence réglementaire spécifique comme Bâle III, cela pourrait affecter la perception de la rigueur et de la clarté des divulgations financières.
+Il s'agit d'un changement structurel qui pourrait nécessiter une enquête plus approfondie pour comprendre pourquoi cet indicateur a été retiré et si cela reflète un changement dans la méthodologie de rapport ou une simplification des divulgations. L'analyste devrait confirmer si cette suppression est intentionnelle et si elle est compensée par d'autres informations ailleurs dans le rapport.</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>Oui</t>
+          <t>Non</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr"/>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-18T18:07:41.005371+00:00</t>
-        </is>
-      </c>
+      <c r="L9" s="3" t="inlineStr"/>
+      <c r="M9" s="3" t="inlineStr"/>
+      <c r="N9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -1056,42 +1004,40 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>FINANCEMENT DE GROS</t>
+          <t>LIENS ENTRE LE RISQUE DE MARCHÉ ET LE BILAN</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>43</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>37</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Note de bas de page</t>
+          <t>Indicateur</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Modification</t>
+          <t>Suppression</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>Comprennent la dette de premier rang qui est assujettie à une conversion au titre du régime de recapitalisation interne des banques. Excluent des billets structurés d’un montant de 3,8 milliards de dollars qui sont assujettis à une conversion au titre du régime de recapitalisation interne des banques (4,4 milliards de dollars au 31 octobre 2024).</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>Comprennent la dette de premier rang qui est assujettie à une conversion au titre du régime de recapitalisation interne des banques. Excluent des billets structurés d’un montant de 2,6 milliards de dollars qui sont assujettis à une conversion au titre du régime de recapitalisation interne des banques (3,3 milliards de dollars au 31 octobre 2025).</t>
-        </is>
-      </c>
+          <t>Participation dans Schwab</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr"/>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>The change in the financial figures for structured notes excluded from conversion affects the bank's risk exposure and capital adequacy, which is critical for regulatory compliance and financial stability analysis.</t>
+          <t>L'indicateur 'Participation dans Schwab' a été retiré du tableau de synthèse des actifs et passifs exposés au risque de marché. Cet indicateur était précédemment inclus pour refléter une participation spécifique dans une entité externe, ce qui peut avoir des implications sur l'exposition au risque de marché et la diversification des actifs.
+La suppression de cet indicateur pourrait indiquer un changement dans la structure des actifs de l'institution, potentiellement dû à une vente ou à une réévaluation de la participation. Cela pourrait affecter les ratios de risque de marché et la manière dont l'institution gère son portefeuille d'investissements, en particulier si cette participation était significative.
+Il s'agit d'un changement structurel qui nécessite une investigation pour comprendre les raisons de cette suppression et son impact sur le profil de risque global de l'institution. L'analyste devrait vérifier si cette suppression est compensée par d'autres ajustements dans le rapport ou si elle reflète un changement stratégique.</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1100,21 +1046,9 @@
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-18T18:09:31.829097+00:00</t>
-        </is>
-      </c>
+      <c r="L10" s="3" t="inlineStr"/>
+      <c r="M10" s="3" t="inlineStr"/>
+      <c r="N10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -1124,17 +1058,17 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>FINANCEMENT DE GROS</t>
+          <t>NOTATIONS DE CRÉDIT¹</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>49</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>43</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1144,22 +1078,20 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Modification</t>
+          <t>Suppression</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>Comprend les dépôts à échéance déterminée d’institutions autres que des banques (non garantis) de 23,9 milliards de dollars (17,3 milliards de dollars au 31 octobre 2024) et les autres dépôts n’ont aucune échéance.</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>Comprend les dépôts à échéance déterminée d’institutions autres que des banques (non garantis) de 36,8 milliards de dollars (26,9 milliards de dollars au 31 octobre 2025) et les autres dépôts n’ont aucune échéance.</t>
-        </is>
-      </c>
+          <t>Après la fin du trimestre, le 22 août 2025, Moody’s a entrepris une révision de la notation des dépôts/de contrepartie et des anciennes dettes de premier rang de la TD en vue d’un rehaussement.</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr"/>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>The significant increase in non-bank term deposits affects liquidity management and risk assessment, which is crucial for strategic financial planning and regulatory reporting.</t>
+          <t>La note de bas de page n°2 a été supprimée du tableau des notations de crédit au T3 2025. Cette note indiquait qu'après la fin du trimestre, le 22 août 2025, Moody’s avait entrepris une révision de la notation des dépôts/de contrepartie et des anciennes dettes de premier rang de la TD en vue d’un rehaussement.
+L'absence de cette note dans le rapport actuel pourrait indiquer que la révision par Moody’s a été finalisée ou que l'information n'est plus pertinente pour le public cible. Cela pourrait avoir un impact sur la perception des investisseurs quant à la stabilité et à la qualité du crédit de la banque, surtout si la révision n'a pas abouti à un rehaussement comme initialement prévu. Les notations de crédit sont cruciales pour évaluer le risque de contrepartie et influencent directement les coûts de financement et les exigences de capital réglementaire selon les normes de Bâle III.
+Il est recommandé que l'analyste confirme si la révision par Moody’s a été complétée et si elle a abouti à un changement de notation. Si la révision est toujours en cours ou a été annulée, cela devrait être clarifié dans le rapport pour éviter toute confusion parmi les parties prenantes. Une investigation plus approfondie pourrait être nécessaire pour comprendre l'impact de cette suppression sur la communication des risques de crédit.</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1180,38 +1112,44 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>FINANCEMENT DE GROS</t>
+          <t>SENSIBILITÉ AU RISQUE DE TAUX D’INTÉRÊT STRUCTUREL – MESURES</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>45</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>39</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Indicateur</t>
+          <t>Note de bas de page</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Suppression</t>
+          <t>Modification</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>Dont : – Total</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr"/>
+          <t>Au 31 juillet 2025, les mesures de sensibilité sont présentées par devise afin de mettre en évidence la sensibilité des produits d’intérêts nets aux variations des taux sous-jacents.</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>N’inclut pas les expositions du secteur Services bancaires de gros.</t>
+        </is>
+      </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>The removal of the 'Dont : – Total' indicator could impact the clarity of the breakdown of totals within the table, affecting the structural understanding of guaranteed versus non-guaranteed components.</t>
+          <t>La note de bas de page n°1 a subi une révision significative dans le tableau de la sensibilité au risque de taux d’intérêt structurel. Initialement, elle décrivait la présentation des mesures de sensibilité par devise pour illustrer la sensibilité des produits d’intérêts nets aux variations des taux. Désormais, elle précise que les expositions du secteur Services bancaires de gros ne sont pas incluses.
+Ce changement a un impact structurel important car il modifie la compréhension de la portée des données présentées. En excluant explicitement les expositions du secteur Services bancaires de gros, la note clarifie les limites des données de sensibilité au risque de taux d’intérêt. Cela peut affecter l'analyse des risques et la prise de décision stratégique, notamment en ce qui concerne la gestion des risques de taux d'intérêt et la conformité aux exigences de Bâle III en matière de gestion des risques.
+Il s'agit d'une mise à jour méthodologique significative. L'analyste devrait confirmer que cette exclusion est cohérente avec les autres sections du rapport et s'assurer que les utilisateurs des états financiers comprennent bien cette limitation. Une investigation plus approfondie pourrait être nécessaire pour évaluer l'impact de cette exclusion sur les ratios prudentiels et la divulgation réglementaire.</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1220,66 +1158,52 @@
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr"/>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M12" s="3" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N12" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-18T18:08:21.346716+00:00</t>
-        </is>
-      </c>
+      <c r="L12" s="3" t="inlineStr"/>
+      <c r="M12" s="3" t="inlineStr"/>
+      <c r="N12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Gestion des risques</t>
+          <t>Gestion du capital</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>NOTATIONS DE CRÉDIT¹</t>
+          <t>ACTIONS ET AUTRES TITRES¹</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>39</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>34</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Note de bas de page</t>
+          <t>Indicateur</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>Après la fin du trimestre, le 22 août 2025, Moody’s a entrepris une révision de la notation des dépôts/de contrepartie et des anciennes dettes de premier rang de la TD en vue d’un rehaussement.</t>
-        </is>
-      </c>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Représentent la notation des dépôts à long terme et la notation du risque de contrepartie attribuées par Moody’s, la notation de crédit d’émetteur attribuée par S&amp;P, la notation des dépôts à long terme de Fitch et la notation d’émetteur à long terme attribuée par DBRS.</t>
+          <t>Billets avec remboursement de capital à recours limité – Série 6⁴</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>This change shifts the focus from a specific credit rating review event to a general description of credit ratings, which may affect how stakeholders perceive the bank's creditworthiness and its communication strategy.</t>
+          <t>L'indicateur "Billets avec remboursement de capital à recours limité – Série 6⁴" a été ajouté dans le tableau de gestion du capital au T1 2026, alors qu'il était absent au T3 2025.
+Cet ajout pourrait refléter l'émission d'une nouvelle série de billets avec remboursement de capital à recours limité, ce qui peut avoir des implications sur la structure du capital et les ratios de fonds propres réglementaires. Les billets avec remboursement de capital à recours limité sont souvent utilisés pour renforcer les fonds propres de catégorie 2, conformément aux exigences de Bâle III.
+Il s'agit d'une mise à jour structurelle importante. L'analyste devrait confirmer que cette nouvelle série est correctement intégrée dans les calculs des ratios de fonds propres et vérifier sa conformité avec les exigences réglementaires en vigueur.</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1288,41 +1212,29 @@
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr"/>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M13" s="3" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N13" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-18T18:09:20.442659+00:00</t>
-        </is>
-      </c>
+      <c r="L13" s="3" t="inlineStr"/>
+      <c r="M13" s="3" t="inlineStr"/>
+      <c r="N13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Gestion des risques</t>
+          <t>Gestion du capital</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>NOTATIONS DE CRÉDIT¹</t>
+          <t>ACTIONS ET AUTRES TITRES¹</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>39</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>34</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -1332,22 +1244,20 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>Représentent la notation des dépôts à long terme et la notation du risque de contrepartie attribuées par Moody’s, la notation de crédit d’émetteur attribuée par S&amp;P, la notation des dépôts à long terme de Fitch et la notation d’émetteur à long terme attribuée par DBRS.</t>
-        </is>
-      </c>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>Comprend a) la dette de premier rang émise avant le 23 septembre 2018; et b) la dette de premier rang émise à partir du 23 septembre 2018, qui est exclue du régime de recapitalisation interne des banques.</t>
+          <t>Pour les BRCRL, série 3, série 4 et série 6, le montant représente l’équivalent en dollars canadiens du montant notionnel en dollars américains.</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>This change alters the understanding of what is included in the senior debt category, which is crucial for assessing the bank's liabilities and compliance with regulatory frameworks.</t>
+          <t>La note de bas de page n-4 a été ajoutée dans le tableau des actions et autres titres au T1 2026.
+Cette note précise que pour les billets avec remboursement de capital à recours limité (BRCRL), série 3, série 4 et série 6, le montant est exprimé en dollars canadiens, bien que le montant notionnel soit en dollars américains. L'ajout de la série 6 indique une nouvelle émission ou une inclusion récente dans le tableau, ce qui peut avoir des implications sur la gestion des risques de change et la structure du capital.
+Il s'agit d'une mise à jour structurelle importante. L'analyste devrait confirmer que cette nouvelle série est correctement intégrée dans les calculs des ratios de fonds propres et vérifier sa conformité avec les exigences réglementaires en vigueur.</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1356,41 +1266,29 @@
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr"/>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-18T18:09:20.590280+00:00</t>
-        </is>
-      </c>
+      <c r="L14" s="3" t="inlineStr"/>
+      <c r="M14" s="3" t="inlineStr"/>
+      <c r="N14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Gestion des risques</t>
+          <t>Gestion du capital</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>NOTATIONS DE CRÉDIT¹</t>
+          <t>ACTIONS ET AUTRES TITRES¹</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>39</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>34</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -1405,17 +1303,19 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Comprend a) la dette de premier rang émise avant le 23 septembre 2018; et b) la dette de premier rang émise à partir du 23 septembre 2018, qui est exclue du régime de recapitalisation interne des banques.</t>
+          <t>Pour plus de renseignements, y compris les caractéristiques de conversion et d’échange, et les distributions, se reporter à la note 20 des états financiers consolidés de 2024 de la Banque.</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Assujettie à une conversion au titre du régime de recapitalisation interne des banques.</t>
+          <t>Pour plus de renseignements, y compris les caractéristiques de conversion et d’échange, les distributions ainsi que les modalités et conditions importantes, se reporter à la note 19 des états financiers consolidés de 2025 de la Banque.</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>This change highlights a regulatory requirement for conversion, which is significant for understanding the bank's obligations and potential impacts on its capital adequacy.</t>
+          <t>La note de bas de page n-1 a été reformulée dans le tableau des actions et autres titres au T1 2026.
+La reformulation inclut désormais des modalités et conditions importantes, en plus des caractéristiques de conversion et d’échange et des distributions. Ce changement élargit la portée des informations fournies, ce qui peut avoir des implications sur la compréhension des investisseurs et des régulateurs concernant les caractéristiques des titres émis par la Banque.
+Il s'agit d'une mise à jour structurelle importante. L'analyste devrait confirmer que cette reformulation est correctement intégrée dans les autres sections du rapport et vérifier sa conformité avec les exigences réglementaires en vigueur.</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1431,22 +1331,22 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Gestion des risques</t>
+          <t>Gestion du capital</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>NOTATIONS DE CRÉDIT¹</t>
+          <t>ACTIONS ET AUTRES TITRES¹</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>39</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>34</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -1456,18 +1356,24 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>Suppression</t>
+          <t>Modification</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>Assujettie à une conversion au titre du régime de recapitalisation interne des banques.</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr"/>
+          <t>Le 31 juillet 2025, la Banque a racheté la totalité de ses 14 millions d’actions privilégiées de premier rang de catégorie A à taux rajusté tous les cinq ans et à dividende non cumulatif comprenant des dispositions relatives aux FPUNV, série 7 (« actions privilégiées de série 7 ») en circulation, à un prix de rachat de 25,00 $ l’action privilégiée de série 7, pour un coût de rachat total d’environ 350 millions de dollars.</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Pour plus de renseignements, se reporter au tableau « Conditions importantes rattachées aux actions privilégiées et autres instruments de capitaux propres » à la note 19 des états financiers consolidés de 2025 de la Banque.</t>
+        </is>
+      </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>The removal of this footnote could indicate a change in the bank's policy or regulatory requirements regarding the conversion of senior debt, which may impact the bank's capital structure and risk management strategy.</t>
+          <t>La note de bas de page n-3 a été reformulée dans le tableau des actions et autres titres au T1 2026.
+La reformulation remplace les détails spécifiques du rachat des actions privilégiées de série 7 par une référence à un tableau de conditions importantes. Ce changement peut affecter la transparence et la clarté des informations fournies aux investisseurs et aux régulateurs, car il nécessite désormais de consulter un autre document pour obtenir des détails précis.
+Il s'agit d'une mise à jour structurelle importante. L'analyste devrait confirmer que cette reformulation est correctement intégrée dans les autres sections du rapport et vérifier sa conformité avec les exigences réglementaires en vigueur.</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1476,41 +1382,29 @@
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr"/>
-      <c r="L16" s="3" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M16" s="3" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N16" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-18T18:09:09.274937+00:00</t>
-        </is>
-      </c>
+      <c r="L16" s="3" t="inlineStr"/>
+      <c r="M16" s="3" t="inlineStr"/>
+      <c r="N16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Gestion des risques</t>
+          <t>Gestion du capital</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>SENSIBILITÉ AU RISQUE DE TAUX D’INTÉRÊT STRUCTUREL – MESURES</t>
+          <t>ACTIONS ET AUTRES TITRES¹</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>39</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -1525,17 +1419,19 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>Au 31 juillet 2025, les mesures de sensibilité sont présentées par devise afin de mettre en évidence la sensibilité des produits d’intérêts nets aux variations des taux sous-jacents.</t>
+          <t>Pour plus de renseignements, se reporter au tableau « Conditions importantes rattachées aux actions privilégiées et autres instruments de capitaux propres » à la note 20 des états financiers consolidés de 2024 de la Banque.</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>N’inclut pas les expositions du secteur Services bancaires de gros.</t>
+          <t>Pour les billets de fonds propres subordonnés perpétuels constituant des autres éléments de fonds propres de catégorie 1 (AT1), le montant représente l’équivalent en dollars canadiens du montant notionnel en dollars de Singapour.</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>The exclusion of exposures from the Wholesale Banking sector represents a significant structural change in the scope of the sensitivity analysis, impacting the interpretation of risk metrics.</t>
+          <t>La note de bas de page n-5 a été reformulée dans le tableau des actions et autres titres au T1 2026.
+La reformulation remplace la référence à un tableau de conditions importantes par des informations spécifiques sur les billets de fonds propres subordonnés perpétuels (AT1), y compris la conversion des montants en dollars canadiens. Ce changement peut avoir des implications sur la compréhension des investisseurs et des régulateurs concernant la structure des fonds propres de la Banque.
+Il s'agit d'une mise à jour structurelle importante. L'analyste devrait confirmer que cette reformulation est correctement intégrée dans les autres sections du rapport et vérifier sa conformité avec les exigences réglementaires en vigueur.</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1571,23 +1467,25 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Indicateur</t>
+          <t>Note de bas de page</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr"/>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>Billets avec remboursement de capital à recours limité – Série 6⁴</t>
-        </is>
-      </c>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>Pour les BRCRL, série 3 et série 4, le montant représente l’équivalent en dollars canadiens du montant notionnel en dollars américains.</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr"/>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>The addition of a new series of capital instruments can impact the bank's capital structure and regulatory capital ratios, which are critical for compliance and financial stability.</t>
+          <t>La note de bas de page n-6 a été supprimée du tableau des actions et autres titres au T1 2026.
+Cette note précisait que pour les BRCRL, série 3 et série 4, le montant était exprimé en dollars canadiens bien que le montant notionnel soit en dollars américains. La suppression de cette note et son remplacement par une nouvelle note incluant la série 6 indique une mise à jour de la structure des BRCRL, ce qui peut avoir des implications sur la gestion des risques de change et la structure du capital.
+Il s'agit d'une mise à jour structurelle importante. L'analyste devrait confirmer que cette nouvelle série est correctement intégrée dans les calculs des ratios de fonds propres et vérifier sa conformité avec les exigences réglementaires en vigueur.</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1596,21 +1494,9 @@
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr"/>
-      <c r="L18" s="3" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M18" s="3" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N18" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-18T18:07:24.685574+00:00</t>
-        </is>
-      </c>
+      <c r="L18" s="3" t="inlineStr"/>
+      <c r="M18" s="3" t="inlineStr"/>
+      <c r="N18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -1620,17 +1506,17 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>ACTIONS ET AUTRES TITRES¹</t>
+          <t>RATIOS CIBLES DE FONDS PROPRES RÉGLEMENTAIRES ET DE TLAC</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>31</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -1645,17 +1531,19 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>Pour plus de renseignements, y compris les caractéristiques de conversion et d’échange, et les distributions, se reporter à la note 20 des états financiers consolidés de 2024 de la Banque.</t>
+          <t>Le plus élevé des suppléments pour les BISI et les banques d’importance systémique mondiale (BISM) s’applique aux fonds propres pondérés en fonction des risques. Le supplément pour les BISI est actuellement équivalent à l’exigence supplémentaire de 1 % relative au ratio de fonds propres sous forme d’actions ordinaires pour les fonds propres pondérés en fonction des risques pour les BISM que doit respecter la Banque. Le supplément pour les BISM pourrait augmenter au-delà de 1 %, si la cote pour les BISM attribuée à la Banque devait augmenter au-delà de certains seuils, pour atteindre un maximum de 4,5 %. La ligne directrice Exigences de levier du BSIF comprend une exigence selon laquelle les BISI doivent maintenir un coussin de ratio de levier fixé à 50 % des exigences pondérées de capacité accrue d’absorption des pertes d’une BISI, soit 0,50 %. Ce coussin s’applique également au ratio de levier TLAC.</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>Pour plus de renseignements, y compris les caractéristiques de conversion et d’échange, les distributions ainsi que les modalités et conditions importantes, se reporter à la note 19 des états financiers consolidés de 2025 de la Banque.</t>
+          <t>Le plus élevé des suppléments pour les BISI et les BISM s’applique aux fonds propres pondérés en fonction des risques. Le supplément pour les BISI est actuellement équivalent à l’exigence supplémentaire de 1 % relative au ratio de fonds propres sous forme d’actions ordinaires pour les fonds propres pondérés en fonction des risques que doit respecter la Banque. Le supplément pour les BISM pourrait augmenter au-delà de 1 %, pour atteindre un maximum de 4 %, si la cote pour les BISM attribuée à la Banque devait augmenter au-delà de certains seuils. La ligne directrice Exigences de levier du BSIF comprend une exigence selon laquelle les BISI doivent maintenir un coussin de ratio de levier fixé à 50 % des exigences pondérées de capacité accrue d’absorption des pertes d’une BISI, soit 0,50 %. Ce coussin s’applique également au ratio de levier TLAC.</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>The addition of terms and conditions information is significant for understanding the full scope of financial instruments, impacting compliance and investor relations.</t>
+          <t>La note de bas de page n°1 a subi une modification significative dans le tableau des ratios cibles de fonds propres réglementaires et de TLAC. Le texte a été révisé pour ajuster le maximum potentiel du supplément pour les BISM de 4,5 % à 4 %. Cette modification est importante car elle touche directement aux exigences de fonds propres pour les banques d’importance systémique mondiale (BISM).
+L'impact de ce changement est notable dans le contexte des exigences de fonds propres sous Bâle III, où les suppléments pour les BISM influencent directement les ratios de fonds propres pondérés en fonction des risques. Une réduction du maximum potentiel de ce supplément pourrait affecter la manière dont la banque gère ses fonds propres et ses stratégies de capitalisation. Cela pourrait également avoir des implications sur la divulgation réglementaire et la conformité avec les lignes directrices du BSIF, notamment en ce qui concerne les exigences de levier.
+Il s'agit d'un changement méthodologique significatif qui pourrait avoir des répercussions sur la gestion du capital de la banque. L'analyste devrait investiguer plus en profondeur pour comprendre les raisons de cette révision et s'assurer que la banque reste conforme aux exigences réglementaires en vigueur. Une vérification de la cohérence avec d'autres divulgations de fonds propres dans le rapport serait également recommandée.</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1664,462 +1552,422 @@
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr"/>
-      <c r="L19" s="3" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M19" s="3" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N19" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-18T18:09:12.321942+00:00</t>
-        </is>
-      </c>
+      <c r="L19" s="3" t="inlineStr"/>
+      <c r="M19" s="3" t="inlineStr"/>
+      <c r="N19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>Gestion du capital</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>ACTIONS ET AUTRES TITRES¹</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>(sans titre)</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>Note de bas de page</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>Modification</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>Le 31 janvier 2025, la Banque a racheté la totalité de ses 20 millions d’actions privilégiées de premier rang de catégorie A à taux rajusté tous les cinq ans et à dividende non cumulatif comprenant des dispositions relatives aux fonds propres d’urgence en cas de non-viabilité (FPUNV), série 5 (« actions privilégiées de série 5 ») en circulation, à un prix de rachat de 25,00 $ l’action privilégiée de série 5, pour un coût de rachat total d’environ 500 millions de dollars.</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>Pour les autres instruments de capitaux propres, le nombre d’actions ou de parts correspond au nombre de billets émis.</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>The change from redemption details to a general statement about equity instruments alters the financial disclosure, affecting transparency and investor understanding.</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr"/>
-      <c r="L20" s="3" t="inlineStr"/>
-      <c r="M20" s="3" t="inlineStr"/>
-      <c r="N20" s="3" t="inlineStr"/>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>Le LCR est calculé conformément à la ligne directrice Normes de liquidité du BSIF, qui tient compte des exigences en matière de liquidité publiées par le CBCB. Le LCR pour le trimestre clos le 31 juillet 2025 représente la moyenne des 64 données quotidiennes du trimestre.</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>Le LCR est calculé conformément à la ligne directrice Normes de liquidité du BSIF, qui tient compte des exigences en matière de liquidité publiées par le CBCB. Le LCR pour le trimestre clos le 31 janvier 2026 représente la moyenne des 61 données quotidiennes du trimestre.</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>La note de bas de page n°1 a subi une modification mineure dans le tableau du ratio de liquidité à court terme, où le nombre de données quotidiennes utilisées pour calculer la moyenne du LCR est passé de 64 à 61 pour le trimestre clos le 31 janvier 2026.
+Ce changement n'affecte pas la méthodologie de calcul du LCR, qui reste conforme aux normes de liquidité du BSIF et aux exigences du CBCB. Il s'agit simplement d'une mise à jour des données utilisées pour le calcul, ce qui est une pratique courante et attendue à chaque trimestre en fonction du nombre de jours ouvrables.
+Il s'agit d'une mise à jour ordinaire qui ne nécessite pas d'investigation approfondie. L'analyste peut confirmer que cette modification est conforme aux pratiques standard de mise à jour des données trimestrielles.</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr"/>
+      <c r="L20" s="4" t="inlineStr"/>
+      <c r="M20" s="4" t="inlineStr"/>
+      <c r="N20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>Gestion du capital</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>ACTIONS ET AUTRES TITRES¹</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>DURÉE CONTRACTUELLE RESTANTE (suite)</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>Note de bas de page</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>Modification</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>Le 31 juillet 2025, la Banque a racheté la totalité de ses 14 millions d’actions privilégiées de premier rang de catégorie A à taux rajusté tous les cinq ans et à dividende non cumulatif comprenant des dispositions relatives aux FPUNV, série 7 (« actions privilégiées de série 7 ») en circulation, à un prix de rachat de 25,00 $ l’action privilégiée de série 7, pour un coût de rachat total d’environ 350 millions de dollars.</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>Pour plus de renseignements, se reporter au tableau « Conditions importantes rattachées aux actions privilégiées et autres instruments de capitaux propres » à la note 19 des états financiers consolidés de 2025 de la Banque.</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>The change from redemption details to a reference for further information alters the financial disclosure, affecting transparency and investor understanding.</t>
-        </is>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="inlineStr"/>
-      <c r="L21" s="3" t="inlineStr"/>
-      <c r="M21" s="3" t="inlineStr"/>
-      <c r="N21" s="3" t="inlineStr"/>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>Comprennent 609 millions de dollars d’engagements de crédit à l’égard de placements dans des actions de sociétés à capital fermé.</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>Comprennent 623 millions de dollars d’engagements de crédit à l’égard de placements dans des actions de sociétés à capital fermé.</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>La note de bas de page n°6 a été modifiée pour refléter une augmentation des engagements de crédit de 609 millions de dollars à 623 millions de dollars concernant les placements dans des actions de sociétés à capital fermé.
+Bien que cette modification représente une augmentation de 14 millions de dollars, elle est relativement mineure par rapport à l'ensemble des engagements de la banque. Cependant, elle pourrait indiquer une légère augmentation de l'exposition au risque de crédit dans le secteur des sociétés à capital fermé, ce qui pourrait avoir des implications sur la gestion du portefeuille de crédit et les stratégies d'investissement.
+Ce changement est principalement cosmétique et ne devrait pas avoir d'impact significatif sur les ratios prudentiels ou les exigences réglementaires. L'analyste peut confirmer cette mise à jour avec les équipes concernées, mais aucune action immédiate n'est requise au-delà de la vérification de la cohérence des chiffres dans les rapports financiers.</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr"/>
+      <c r="L21" s="4" t="inlineStr"/>
+      <c r="M21" s="4" t="inlineStr"/>
+      <c r="N21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>Gestion du capital</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>ACTIONS ET AUTRES TITRES¹</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>FINANCEMENT DE GROS</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>Note de bas de page</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>Modification</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>Pour les autres instruments de capitaux propres, le nombre d’actions ou de parts correspond au nombre de billets émis.</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>Pour les BRCRL, série 3, série 4 et série 6, le montant représente l’équivalent en dollars canadiens du montant notionnel en dollars américains.</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>The specification of currency conversion details is significant for financial reporting accuracy and investor understanding of capital instruments.</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr"/>
-      <c r="L22" s="3" t="inlineStr"/>
-      <c r="M22" s="3" t="inlineStr"/>
-      <c r="N22" s="3" t="inlineStr"/>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>Comprennent la dette de premier rang qui est assujettie à une conversion au titre du régime de recapitalisation interne des banques. Excluent des billets structurés d’un montant de 3,8 milliards de dollars qui sont assujettis à une conversion au titre du régime de recapitalisation interne des banques (4,4 milliards de dollars au 31 octobre 2024).</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>Comprennent la dette de premier rang qui est assujettie à une conversion au titre du régime de recapitalisation interne des banques. Excluent des billets structurés d’un montant de 2,6 milliards de dollars qui sont assujettis à une conversion au titre du régime de recapitalisation interne des banques (3,3 milliards de dollars au 31 octobre 2025).</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>La note de bas de page n°4 a subi une modification dans le tableau du financement de gros. Le texte a été mis à jour pour refléter des montants révisés concernant les billets structurés exclus de la conversion au titre du régime de recapitalisation interne des banques. Les montants sont passés de 3,8 milliards de dollars à 2,6 milliards de dollars, et les références de date ont été ajustées de 2024 à 2025.
+Cette modification n'a pas d'impact direct sur les exigences réglementaires telles que Bâle III, mais elle peut influencer la perception des investisseurs et des analystes sur la gestion des risques de l'institution. Les montants révisés peuvent indiquer des changements dans la structure de financement ou des ajustements dans la stratégie de gestion des risques, bien que cela ne soit pas explicitement lié à une méthodologie de calcul ou à une divulgation réglementaire.
+Il s'agit d'une mise à jour ordinaire des montants financiers qui ne nécessite pas d'investigation approfondie. Cependant, l'analyste devrait confirmer que ces ajustements sont cohérents avec les autres sections du rapport et qu'ils reflètent fidèlement la situation financière actuelle de l'institution.</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr"/>
+      <c r="L22" s="4" t="inlineStr"/>
+      <c r="M22" s="4" t="inlineStr"/>
+      <c r="N22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>Gestion du capital</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>ACTIONS ET AUTRES TITRES¹</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>FINANCEMENT DE GROS</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>Note de bas de page</t>
         </is>
       </c>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>Modification</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>Pour plus de renseignements, se reporter au tableau « Conditions importantes rattachées aux actions privilégiées et autres instruments de capitaux propres » à la note 20 des états financiers consolidés de 2024 de la Banque.</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>Pour les billets de fonds propres subordonnés perpétuels constituant des autres éléments de fonds propres de catégorie 1 (AT1), le montant représente l’équivalent en dollars canadiens du montant notionnel en dollars de Singapour.</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>The specification of currency conversion details for AT1 notes is significant for financial reporting accuracy and investor understanding of capital instruments.</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr"/>
-      <c r="L23" s="3" t="inlineStr"/>
-      <c r="M23" s="3" t="inlineStr"/>
-      <c r="N23" s="3" t="inlineStr"/>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>Comprend les dépôts à échéance déterminée d’institutions autres que des banques (non garantis) de 23,9 milliards de dollars (17,3 milliards de dollars au 31 octobre 2024) et les autres dépôts n’ont aucune échéance.</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>Comprend les dépôts à échéance déterminée d’institutions autres que des banques (non garantis) de 36,8 milliards de dollars (26,9 milliards de dollars au 31 octobre 2025) et les autres dépôts n’ont aucune échéance.</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>La note de bas de page n°6 a été modifiée dans le tableau du financement de gros. Le texte a été mis à jour pour indiquer une augmentation significative des dépôts à échéance déterminée d’institutions autres que des banques, passant de 23,9 milliards de dollars à 36,8 milliards de dollars. Les montants pour l'année de référence ont également été ajustés de 17,3 milliards de dollars à 26,9 milliards de dollars.
+Bien que cette modification ne soit pas directement liée à une exigence réglementaire spécifique, elle peut avoir des implications sur la perception de la liquidité et de la stabilité financière de l'institution. Une augmentation des dépôts non garantis peut signaler une dépendance accrue à des sources de financement potentiellement plus volatiles, ce qui pourrait être pertinent pour les évaluations de risque par les parties prenantes.
+Il s'agit d'une mise à jour ordinaire des montants financiers. L'analyste devrait vérifier que ces chiffres sont cohérents avec les autres sections du rapport et qu'ils reflètent fidèlement la situation financière actuelle de l'institution. Aucune action immédiate n'est requise, mais une surveillance continue est recommandée.</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr"/>
+      <c r="L23" s="4" t="inlineStr"/>
+      <c r="M23" s="4" t="inlineStr"/>
+      <c r="N23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>Gestion du capital</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>ACTIONS ET AUTRES TITRES¹</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>Indicateur</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>SOMMAIRE DES ACTIFS LIQUIDES MOYENS NON GREVÉS DÉTENUS PAR LA BANQUE, LES FILIALES ET LES SUCCURSALES</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Note de bas de page</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
         <is>
           <t>Suppression</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>Série 5²</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr"/>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>The removal of a series of preferred shares can affect the bank's equity structure and investor relations, potentially impacting dividend policies and capital adequacy.</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr"/>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N24" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-18T18:07:36.224563+00:00</t>
-        </is>
-      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>Comprennent les titres adossés à des créances hypothécaires en vertu de la Loi nationale sur l’habitation.</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr"/>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>La suppression d'une ancienne note de bas de page sans contexte détaillé nécessite une vérification manuelle pour confirmer son impact.</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr"/>
+      <c r="L24" s="4" t="inlineStr"/>
+      <c r="M24" s="4" t="inlineStr"/>
+      <c r="N24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>Gestion du capital</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>ACTIONS ET AUTRES TITRES¹</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>SOMMAIRE DES ACTIFS LIQUIDES NON GREVÉS DÉTENUS PAR LA BANQUE, LES FILIALES ET LES SUCCURSALES</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>Note de bas de page</t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr"/>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>Comprennent les titres adossés à des créances hypothécaires en vertu de la Loi nationale sur l’habitation.</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>L'ajout d'une nouvelle note de bas de page sans contexte détaillé nécessite une vérification manuelle pour confirmer son impact.</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr"/>
+      <c r="L25" s="4" t="inlineStr"/>
+      <c r="M25" s="4" t="inlineStr"/>
+      <c r="N25" s="4" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>SOMMAIRE DU FINANCEMENT PROVENANT DES DÉPÔTS</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Note de bas de page</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>Suppression</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>Le 18 décembre 2024, la Banque a émis des billets avec remboursement de capital à recours limité d’un montant en capital de 750 millions de dollars à taux fixe rajusté à 5,909 % comprenant des dispositions relatives aux FPUNV, série 5 (les « BRCRL »). Les BRCRL porteront intérêt au taux de 5,909 % par année, payable trimestriellement, pour la période initiale se terminant le 1er janvier 2030, exclusivement. Par la suite, le taux d’intérêt sur les BRCRL sera rajusté tous les cinq ans à un taux correspondant au rendement des obligations du gouvernement du Canada alors en vigueur, majoré de 3,10 %. Les BRCRL viendront à échéance le 1er janvier 2085. Parallèlement à l’émission des BRCRL, la Banque a émis 750 000 actions privilégiées à taux fixe rajusté à 5,909 % et à dividende non cumulatif comprenant des dispositions relatives aux FPUNV, série 32 (« actions privilégiées de série 32 »). Les actions privilégiées de série 32 sont éliminées des états financiers consolidés de la Banque.</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr"/>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>The removal of detailed issuance information can affect transparency and investor understanding of the bank's capital structure and financial instruments.</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr"/>
-      <c r="L25" s="3" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M25" s="3" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N25" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-18T18:09:04.945140+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>Gestion du capital</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>ACTIONS ET AUTRES TITRES¹</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>Note de bas de page</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>Suppression</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>Pour les billets de fonds propres subordonnés perpétuels (AT1), le montant représente l’équivalent en dollars canadiens du montant notionnel en dollars de Singapour.</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr"/>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>The removal of this footnote could impact the understanding of currency conversion for perpetual subordinated capital notes, which is important for accurate financial reporting and analysis.</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr"/>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N26" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-18T18:09:11.928472+00:00</t>
-        </is>
-      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>¹ La méthode de calcul a été modifiée pour tenir compte du financement provenant des dépôts généré par les services bancaires personnels et commerciaux et les activités de gestion de patrimoine.</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr"/>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>La suppression d'une ancienne note de bas de page sans contexte détaillé nécessite une vérification manuelle pour confirmer son impact.</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr"/>
+      <c r="L26" s="4" t="inlineStr"/>
+      <c r="M26" s="4" t="inlineStr"/>
+      <c r="N26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Gestion des risques</t>
+          <t>Gestion du capital</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>SOMMAIRE DES ACTIFS LIQUIDES MOYENS NON GREVÉS DÉTENUS PAR LA BANQUE, LES FILIALES ET LES SUCCURSALES</t>
+          <t>ACTIONS ET AUTRES TITRES¹</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>39</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>34</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Note de bas de page</t>
+          <t>Indicateur</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -2129,13 +1977,15 @@
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>Comprennent les titres adossés à des créances hypothécaires en vertu de la Loi nationale sur l’habitation.</t>
+          <t>Série 5²</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>La suppression d'une ancienne note de bas de page sans contexte détaillé nécessite une vérification manuelle pour confirmer son impact.</t>
+          <t>L'indicateur "Série 5²" a été supprimé du tableau de gestion du capital au T1 2026, alors qu'il était présent au T3 2025.
+La suppression de cet indicateur pourrait indiquer que la série d'actions privilégiées correspondante a été rachetée ou convertie, ce qui peut affecter la composition des fonds propres de la banque. Cependant, l'impact sur les ratios de fonds propres est probablement limité, car il s'agit d'une série spécifique parmi plusieurs autres.
+Il s'agit d'une mise à jour ordinaire. L'analyste devrait vérifier que cette suppression est correctement reflétée dans les autres sections du rapport et s'assurer qu'elle n'affecte pas les divulgations réglementaires.</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -2144,62 +1994,52 @@
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr"/>
-      <c r="L27" s="4" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M27" s="4" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N27" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-18T18:09:37.640911+00:00</t>
-        </is>
-      </c>
+      <c r="L27" s="4" t="inlineStr"/>
+      <c r="M27" s="4" t="inlineStr"/>
+      <c r="N27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Gestion des risques</t>
+          <t>Gestion du capital</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>SOMMAIRE DES ACTIFS LIQUIDES NON GREVÉS DÉTENUS PAR LA BANQUE, LES FILIALES ET LES SUCCURSALES</t>
+          <t>ACTIONS ET AUTRES TITRES¹</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>39</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>34</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>Note de bas de page</t>
+          <t>Indicateur</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="G28" s="4" t="inlineStr"/>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>Comprennent les titres adossés à des créances hypothécaires en vertu de la Loi nationale sur l’habitation.</t>
-        </is>
-      </c>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>Série 7³</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr"/>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>L'ajout d'une nouvelle note de bas de page sans contexte détaillé nécessite une vérification manuelle pour confirmer son impact.</t>
+          <t>L'indicateur "Série 7³" a été supprimé du tableau de gestion du capital au T1 2026, alors qu'il était présent au T3 2025.
+Cette suppression pourrait indiquer que la série d'actions privilégiées a été rachetée, annulée ou convertie. Bien que cela puisse avoir un impact sur la structure des fonds propres, l'effet sur les ratios globaux est probablement mineur, étant donné qu'il s'agit d'une série parmi d'autres.
+Il s'agit d'une mise à jour ordinaire. L'analyste devrait confirmer que cette suppression est correctement reflétée dans les autres sections du rapport et s'assurer qu'elle n'affecte pas les exigences de divulgation réglementaire.</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -2208,41 +2048,29 @@
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr"/>
-      <c r="L28" s="4" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M28" s="4" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N28" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-18T18:08:29.024930+00:00</t>
-        </is>
-      </c>
+      <c r="L28" s="4" t="inlineStr"/>
+      <c r="M28" s="4" t="inlineStr"/>
+      <c r="N28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Gestion des risques</t>
+          <t>Gestion du capital</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>SOMMAIRE DU FINANCEMENT PROVENANT DES DÉPÔTS</t>
+          <t>ACTIONS ET AUTRES TITRES¹</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>39</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>34</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -2257,13 +2085,15 @@
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>¹ La méthode de calcul a été modifiée pour tenir compte du financement provenant des dépôts généré par les services bancaires personnels et commerciaux et les activités de gestion de patrimoine.</t>
+          <t>Le 31 janvier 2025, la Banque a racheté la totalité de ses 20 millions d’actions privilégiées de premier rang de catégorie A à taux rajusté tous les cinq ans et à dividende non cumulatif comprenant des dispositions relatives aux fonds propres d’urgence en cas de non-viabilité (FPUNV), série 5 (« actions privilégiées de série 5 ») en circulation, à un prix de rachat de 25,00 $ l’action privilégiée de série 5, pour un coût de rachat total d’environ 500 millions de dollars.</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>La suppression d'une ancienne note de bas de page sans contexte détaillé nécessite une vérification manuelle pour confirmer son impact.</t>
+          <t>La note de bas de page n-2 a été supprimée du tableau des actions et autres titres au T1 2026.
+Cette note détaillait le rachat par la Banque de ses actions privilégiées de série 5, ce qui a eu lieu le 31 janvier 2025. La suppression de cette note indique que l'événement est désormais considéré comme historique et n'est plus pertinent pour le tableau actuel. Cela n'affecte pas directement les ratios de fonds propres actuels, mais il est important de s'assurer que toutes les implications de ce rachat ont été correctement intégrées dans les états financiers précédents.
+Il s'agit d'une mise à jour ordinaire. L'analyste devrait vérifier que cette suppression est correctement reflétée dans les autres sections du rapport et s'assurer qu'elle n'affecte pas les divulgations réglementaires.</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -2272,21 +2102,9 @@
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr"/>
-      <c r="L29" s="4" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M29" s="4" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N29" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-18T18:08:34.008361+00:00</t>
-        </is>
-      </c>
+      <c r="L29" s="4" t="inlineStr"/>
+      <c r="M29" s="4" t="inlineStr"/>
+      <c r="N29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -2296,18 +2114,22 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>TOTAL DE L’EXPOSITION NETTE PAR RÉGION ET CONTREPARTIE</t>
+          <t>ACTIONS ET AUTRES TITRES¹</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr"/>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Tableau</t>
+          <t>Note de bas de page</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -2317,15 +2139,15 @@
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>TOTAL DE L’EXPOSITION NETTE PAR RÉGION ET CONTREPARTIE</t>
+          <t>Le 18 décembre 2024, la Banque a émis des billets avec remboursement de capital à recours limité d’un montant en capital de 750 millions de dollars à taux fixe rajusté à 5,909 % comprenant des dispositions relatives aux FPUNV, série 5 (les « BRCRL »). Les BRCRL porteront intérêt au taux de 5,909 % par année, payable trimestriellement, pour la période initiale se terminant le 1er janvier 2030, exclusivement. Par la suite, le taux d’intérêt sur les BRCRL sera rajusté tous les cinq ans à un taux correspondant au rendement des obligations du gouvernement du Canada alors en vigueur, majoré de 3,10 %. Les BRCRL viendront à échéance le 1er janvier 2085. Parallèlement à l’émission des BRCRL, la Banque a émis 750 000 actions privilégiées à taux fixe rajusté à 5,909 % et à dividende non cumulatif comprenant des dispositions relatives aux FPUNV, série 32 (« actions privilégiées de série 32 »). Les actions privilégiées de série 32 sont éliminées des états financiers consolidés de la Banque.</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>Le changement constaté concerne la suppression d'un tableau intitulé 'TOTAL DE L’EXPOSITION NETTE PAR RÉGION ET CONTREPARTIE' dans la section de gestion du capital. Ce tableau fournissait des informations détaillées sur l'exposition nette de la banque par région, incluant l'Europe, le Royaume-Uni, l'Asie, et d'autres régions. La suppression de ce tableau peut indiquer un changement dans la manière dont la banque divulgue ses expositions géographiques, ce qui pourrait avoir des implications sur la transparence et la compréhension des risques géographiques par les parties prenantes.
-D'un point de vue réglementaire, la divulgation des expositions par région est souvent requise pour évaluer la concentration des risques et la diversification géographique, conformément aux exigences de Bâle III et aux lignes directrices du BSIF. La suppression de ce tableau pourrait donc affecter la capacité des régulateurs et des investisseurs à évaluer correctement le profil de risque de la banque. Il est crucial de comprendre si cette suppression est compensée par d'autres divulgations ou si elle résulte d'un changement méthodologique.
-Il est recommandé d'investiguer ce changement pour déterminer s'</t>
+          <t>La note de bas de page n-7 a été supprimée du tableau des actions et autres titres au T1 2026.
+Cette note détaillait l'émission par la Banque de billets avec remboursement de capital à recours limité (BRCRL) série 5, ainsi que les conditions associées. La suppression de cette note indique que l'information est désormais considérée comme historique et n'est plus pertinente pour le tableau actuel. Cela n'affecte pas directement les ratios de fonds propres actuels, mais il est important de s'assurer que toutes les implications de cette émission ont été correctement intégrées dans les états financiers précédents.
+Il s'agit d'une mise à jour ordinaire. L'analyste devrait vérifier que cette suppression est correctement reflétée dans les autres sections du rapport et s'assurer qu'elle n'affecte pas les divulgations réglementaires.</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -2338,8 +2160,112 @@
       <c r="M30" s="4" t="inlineStr"/>
       <c r="N30" s="4" t="inlineStr"/>
     </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Gestion du capital</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>ACTIONS ET AUTRES TITRES¹</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>Note de bas de page</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>Pour les billets de fonds propres subordonnés perpétuels (AT1), le montant représente l’équivalent en dollars canadiens du montant notionnel en dollars de Singapour.</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr"/>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>La note de bas de page n-8 a été supprimée du tableau des actions et autres titres au T1 2026.
+Cette note précisait que pour les billets de fonds propres subordonnés perpétuels (AT1), le montant était exprimé en dollars canadiens bien que le montant notionnel soit en dollars de Singapour. La suppression de cette note indique que l'information est désormais considérée comme historique et n'est plus pertinente pour le tableau actuel. Cela n'affecte pas directement les ratios de fonds propres actuels, mais il est important de s'assurer que toutes les implications de ces billets ont été correctement intégrées dans les états financiers précédents.
+Il s'agit d'une mise à jour ordinaire. L'analyste devrait vérifier que cette suppression est correctement reflétée dans les autres sections du rapport et s'assurer qu'elle n'affecte pas les divulgations réglementaires.</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="inlineStr"/>
+      <c r="L31" s="4" t="inlineStr"/>
+      <c r="M31" s="4" t="inlineStr"/>
+      <c r="N31" s="4" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Gestion du capital</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL DE L’EXPOSITION NETTE PAR RÉGION ET CONTREPARTIE</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr"/>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>Tableau</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL DE L’EXPOSITION NETTE PAR RÉGION ET CONTREPARTIE</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr"/>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>Le changement constaté concerne la suppression d'un tableau intitulé 'TOTAL DE L’EXPOSITION NETTE PAR RÉGION ET CONTREPARTIE' dans la section de gestion du capital. Ce tableau fournissait des informations détaillées sur l'exposition nette de la banque par région, incluant des régions spécifiques comme l'Europe, le Royaume-Uni, l'Asie, et d'autres. La suppression de ce tableau pourrait indiquer un changement dans la manière dont la banque divulgue ses expositions géographiques, ce qui peut avoir des implications sur la transparence et la gestion des risques géographiques.
+D'un point de vue réglementaire, la divulgation des expositions par région est souvent requise pour évaluer la concentration des risques et la diversification géographique, ce qui est crucial pour la gestion du capital et la conformité aux normes prudentielles telles que Bâle III. La suppression de ce tableau pourrait signifier un changement dans la stratégie de divulgation ou une révision des exigences réglementaires, ce qui nécessite une attention particulière pour s'assurer que la banque reste conforme aux attentes du BSIF et des autres régulateurs.
+Il est recommandé d'investiguer ce changement pour comprendre</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr"/>
+      <c r="L32" s="4" t="inlineStr"/>
+      <c r="M32" s="4" t="inlineStr"/>
+      <c r="N32" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N30"/>
+  <autoFilter ref="A1:N32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/resultats/td/2026_t1_vs_2025_t3/comparison.xlsx
+++ b/outputs/resultats/td/2026_t1_vs_2025_t3/comparison.xlsx
@@ -988,7 +988,7 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr"/>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr"/>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr"/>
@@ -2249,9 +2249,9 @@
       <c r="H32" s="4" t="inlineStr"/>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>Le changement constaté concerne la suppression d'un tableau intitulé 'TOTAL DE L’EXPOSITION NETTE PAR RÉGION ET CONTREPARTIE' dans la section de gestion du capital. Ce tableau fournissait des informations détaillées sur l'exposition nette de la banque par région, incluant des régions spécifiques comme l'Europe, le Royaume-Uni, l'Asie, et d'autres. La suppression de ce tableau pourrait indiquer un changement dans la manière dont la banque divulgue ses expositions géographiques, ce qui peut avoir des implications sur la transparence et la gestion des risques géographiques.
-D'un point de vue réglementaire, la divulgation des expositions par région est souvent requise pour évaluer la concentration des risques et la diversification géographique, ce qui est crucial pour la gestion du capital et la conformité aux normes prudentielles telles que Bâle III. La suppression de ce tableau pourrait signifier un changement dans la stratégie de divulgation ou une révision des exigences réglementaires, ce qui nécessite une attention particulière pour s'assurer que la banque reste conforme aux attentes du BSIF et des autres régulateurs.
-Il est recommandé d'investiguer ce changement pour comprendre</t>
+          <t>Le changement constaté concerne la suppression d'un tableau intitulé 'TOTAL DE L’EXPOSITION NETTE PAR RÉGION ET CONTREPARTIE' dans la section de gestion du capital. Ce tableau fournissait des informations détaillées sur l'exposition nette de la banque par région, incluant des régions spécifiques comme l'Europe, le Royaume-Uni, l'Asie, et d'autres. La suppression de ce tableau peut indiquer un changement dans la manière dont la banque divulgue ses expositions géographiques, ce qui pourrait avoir des implications sur la transparence et la gestion des risques géographiques.
+D'un point de vue réglementaire, la divulgation de l'exposition par région est souvent requise pour évaluer la concentration des risques et la diversification géographique, ce qui est crucial pour la gestion du capital et le respect des exigences de Bâle III. La suppression de ce tableau pourrait signifier un changement dans la stratégie de divulgation ou une révision des méthodes de calcul des expositions, ce qui nécessite une attention particulière pour s'assurer que la banque reste conforme aux exigences de divulgation réglementaire.
+Il est recommandé d'investiguer ce changement pour comprendre les raisons der</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">

--- a/outputs/resultats/td/2026_t1_vs_2025_t3/comparison.xlsx
+++ b/outputs/resultats/td/2026_t1_vs_2025_t3/comparison.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Changements détectés" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Changements détectés'!$A$1:$N$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Changements détectés'!$A$1:$M$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N32"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -469,11 +469,10 @@
     <col width="50" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="70" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
     <col width="30" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -524,7 +523,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Nouvelle divulgation ?</t>
+          <t>Nouvelle idée ?</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -538,11 +537,6 @@
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Validé par</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Validé le</t>
         </is>
@@ -600,7 +594,6 @@
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -652,13 +645,12 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>Oui</t>
+          <t>Non</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
-      <c r="N3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -710,13 +702,12 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>Oui</t>
+          <t>Non</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr"/>
       <c r="L4" s="3" t="inlineStr"/>
       <c r="M4" s="3" t="inlineStr"/>
-      <c r="N4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -768,13 +759,12 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>Oui</t>
+          <t>Non</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
-      <c r="N5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -822,13 +812,12 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>Oui</t>
+          <t>Non</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr"/>
       <c r="L6" s="3" t="inlineStr"/>
       <c r="M6" s="3" t="inlineStr"/>
-      <c r="N6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -886,7 +875,6 @@
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
-      <c r="N7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -940,7 +928,6 @@
       <c r="K8" s="3" t="inlineStr"/>
       <c r="L8" s="3" t="inlineStr"/>
       <c r="M8" s="3" t="inlineStr"/>
-      <c r="N8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -988,13 +975,12 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>Oui</t>
+          <t>Non</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr"/>
       <c r="L9" s="3" t="inlineStr"/>
       <c r="M9" s="3" t="inlineStr"/>
-      <c r="N9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -1048,7 +1034,6 @@
       <c r="K10" s="3" t="inlineStr"/>
       <c r="L10" s="3" t="inlineStr"/>
       <c r="M10" s="3" t="inlineStr"/>
-      <c r="N10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -1102,7 +1087,6 @@
       <c r="K11" s="3" t="inlineStr"/>
       <c r="L11" s="3" t="inlineStr"/>
       <c r="M11" s="3" t="inlineStr"/>
-      <c r="N11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1160,7 +1144,6 @@
       <c r="K12" s="3" t="inlineStr"/>
       <c r="L12" s="3" t="inlineStr"/>
       <c r="M12" s="3" t="inlineStr"/>
-      <c r="N12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -1214,7 +1197,6 @@
       <c r="K13" s="3" t="inlineStr"/>
       <c r="L13" s="3" t="inlineStr"/>
       <c r="M13" s="3" t="inlineStr"/>
-      <c r="N13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -1268,7 +1250,6 @@
       <c r="K14" s="3" t="inlineStr"/>
       <c r="L14" s="3" t="inlineStr"/>
       <c r="M14" s="3" t="inlineStr"/>
-      <c r="N14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -1326,7 +1307,6 @@
       <c r="K15" s="3" t="inlineStr"/>
       <c r="L15" s="3" t="inlineStr"/>
       <c r="M15" s="3" t="inlineStr"/>
-      <c r="N15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -1384,7 +1364,6 @@
       <c r="K16" s="3" t="inlineStr"/>
       <c r="L16" s="3" t="inlineStr"/>
       <c r="M16" s="3" t="inlineStr"/>
-      <c r="N16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -1442,7 +1421,6 @@
       <c r="K17" s="3" t="inlineStr"/>
       <c r="L17" s="3" t="inlineStr"/>
       <c r="M17" s="3" t="inlineStr"/>
-      <c r="N17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -1496,7 +1474,6 @@
       <c r="K18" s="3" t="inlineStr"/>
       <c r="L18" s="3" t="inlineStr"/>
       <c r="M18" s="3" t="inlineStr"/>
-      <c r="N18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -1554,7 +1531,6 @@
       <c r="K19" s="3" t="inlineStr"/>
       <c r="L19" s="3" t="inlineStr"/>
       <c r="M19" s="3" t="inlineStr"/>
-      <c r="N19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -1612,7 +1588,6 @@
       <c r="K20" s="4" t="inlineStr"/>
       <c r="L20" s="4" t="inlineStr"/>
       <c r="M20" s="4" t="inlineStr"/>
-      <c r="N20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -1670,7 +1645,6 @@
       <c r="K21" s="4" t="inlineStr"/>
       <c r="L21" s="4" t="inlineStr"/>
       <c r="M21" s="4" t="inlineStr"/>
-      <c r="N21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -1722,13 +1696,12 @@
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>Oui</t>
+          <t>Non</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr"/>
       <c r="L22" s="4" t="inlineStr"/>
       <c r="M22" s="4" t="inlineStr"/>
-      <c r="N22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -1780,13 +1753,12 @@
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>Oui</t>
+          <t>Non</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr"/>
       <c r="L23" s="4" t="inlineStr"/>
       <c r="M23" s="4" t="inlineStr"/>
-      <c r="N23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -1838,7 +1810,6 @@
       <c r="K24" s="4" t="inlineStr"/>
       <c r="L24" s="4" t="inlineStr"/>
       <c r="M24" s="4" t="inlineStr"/>
-      <c r="N24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -1890,7 +1861,6 @@
       <c r="K25" s="4" t="inlineStr"/>
       <c r="L25" s="4" t="inlineStr"/>
       <c r="M25" s="4" t="inlineStr"/>
-      <c r="N25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -1942,7 +1912,6 @@
       <c r="K26" s="4" t="inlineStr"/>
       <c r="L26" s="4" t="inlineStr"/>
       <c r="M26" s="4" t="inlineStr"/>
-      <c r="N26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -1996,7 +1965,6 @@
       <c r="K27" s="4" t="inlineStr"/>
       <c r="L27" s="4" t="inlineStr"/>
       <c r="M27" s="4" t="inlineStr"/>
-      <c r="N27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -2050,7 +2018,6 @@
       <c r="K28" s="4" t="inlineStr"/>
       <c r="L28" s="4" t="inlineStr"/>
       <c r="M28" s="4" t="inlineStr"/>
-      <c r="N28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -2104,7 +2071,6 @@
       <c r="K29" s="4" t="inlineStr"/>
       <c r="L29" s="4" t="inlineStr"/>
       <c r="M29" s="4" t="inlineStr"/>
-      <c r="N29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -2158,7 +2124,6 @@
       <c r="K30" s="4" t="inlineStr"/>
       <c r="L30" s="4" t="inlineStr"/>
       <c r="M30" s="4" t="inlineStr"/>
-      <c r="N30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -2212,7 +2177,6 @@
       <c r="K31" s="4" t="inlineStr"/>
       <c r="L31" s="4" t="inlineStr"/>
       <c r="M31" s="4" t="inlineStr"/>
-      <c r="N31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -2249,9 +2213,7 @@
       <c r="H32" s="4" t="inlineStr"/>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>Le changement constaté concerne la suppression d'un tableau intitulé 'TOTAL DE L’EXPOSITION NETTE PAR RÉGION ET CONTREPARTIE' dans la section de gestion du capital. Ce tableau fournissait des informations détaillées sur l'exposition nette de la banque par région, incluant des régions spécifiques comme l'Europe, le Royaume-Uni, l'Asie, et d'autres. La suppression de ce tableau peut indiquer un changement dans la manière dont la banque divulgue ses expositions géographiques, ce qui pourrait avoir des implications sur la transparence et la gestion des risques géographiques.
-D'un point de vue réglementaire, la divulgation de l'exposition par région est souvent requise pour évaluer la concentration des risques et la diversification géographique, ce qui est crucial pour la gestion du capital et le respect des exigences de Bâle III. La suppression de ce tableau pourrait signifier un changement dans la stratégie de divulgation ou une révision des méthodes de calcul des expositions, ce qui nécessite une attention particulière pour s'assurer que la banque reste conforme aux exigences de divulgation réglementaire.
-Il est recommandé d'investiguer ce changement pour comprendre les raisons der</t>
+          <t>OUI, la suppression du tableau 'TOTAL DE L’EXPOSITION NETTE PAR RÉGION ET CONTREPARTIE' modifie la structure du rapport. Cela affecte la visibilité sur la répartition géographique des expositions, ce qui est pertinent pour l'analyse des risques régionaux.</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2262,10 +2224,9 @@
       <c r="K32" s="4" t="inlineStr"/>
       <c r="L32" s="4" t="inlineStr"/>
       <c r="M32" s="4" t="inlineStr"/>
-      <c r="N32" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N32"/>
+  <autoFilter ref="A1:M32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>